--- a/timeTable_EE.xlsx
+++ b/timeTable_EE.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D8F643A-2780-4AA7-B017-394854E65F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B1EB49-C40B-4484-AB12-AD9F3BB1667B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="4005" windowWidth="19290" windowHeight="10755" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="4050" windowWidth="21705" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="s2" sheetId="1" r:id="rId1"/>
-    <sheet name="s3" sheetId="2" r:id="rId2"/>
-    <sheet name="s4" sheetId="3" r:id="rId3"/>
-    <sheet name="s5" sheetId="4" r:id="rId4"/>
-    <sheet name="s6" sheetId="5" r:id="rId5"/>
-    <sheet name="s7" sheetId="6" r:id="rId6"/>
-    <sheet name="s8" sheetId="7" r:id="rId7"/>
-    <sheet name="s1" sheetId="8" r:id="rId8"/>
+    <sheet name="s1" sheetId="1" r:id="rId1"/>
+    <sheet name="s2" sheetId="2" r:id="rId2"/>
+    <sheet name="s3" sheetId="3" r:id="rId3"/>
+    <sheet name="s4" sheetId="4" r:id="rId4"/>
+    <sheet name="s5" sheetId="5" r:id="rId5"/>
+    <sheet name="s6" sheetId="6" r:id="rId6"/>
+    <sheet name="s7" sheetId="7" r:id="rId7"/>
+    <sheet name="s8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="14">
   <si>
     <t>week_day</t>
   </si>
@@ -54,12 +54,6 @@
   </si>
   <si>
     <t>monday</t>
-  </si>
-  <si>
-    <t>GAMAT101</t>
-  </si>
-  <si>
-    <t>GAPHT121</t>
   </si>
   <si>
     <t>FREE</t>
@@ -90,10 +84,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,12 +97,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -118,15 +126,15 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -149,44 +157,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -213,32 +221,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -265,24 +255,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -294,151 +266,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,142 +465,142 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1FE0967-0AA7-4746-9EF7-98724D81DF3A}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,129 +631,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -766,11 +762,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD38099-D27A-4F3F-95F7-701874DDD435}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,129 +797,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -932,11 +928,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F8CC29-4A62-4D57-B66B-0B5A4997A9A1}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,129 +963,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1098,11 +1094,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E836F3C2-97F2-4FE2-9766-AE30DBBC4392}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,143 +1129,142 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77967C2F-DB8A-4A5C-9D75-743D1D308E04}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,129 +1295,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1431,11 +1426,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3387BD79-7144-449C-9FEF-BD281D39156B}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1466,129 +1461,129 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1597,11 +1592,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABC4B9C-E6E8-45AD-80F0-64E3C7CB7EB0}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,127 +1633,126 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>